--- a/zini-q7m2/Zini_My_Expressions.xlsx
+++ b/zini-q7m2/Zini_My_Expressions.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="My Expressions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'My Expressions'!$A$1:$D$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'My Expressions'!$A$1:$D$92</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1643,225 +1643,751 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>Class 7</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>일상·사교</t>
+          <t>협상·거래</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Intro &amp; Warm-Up</t>
+          <t>We're still waiting on ~</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>자기소개</t>
+          <t>아직 ~를 기다리는 중이에요</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>Class 7</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>일상·사교</t>
+          <t>협상·거래</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Brian introduces himself — then your</t>
+          <t>It's confirmed that ~</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>인도네시아 생활</t>
+          <t>~가 확정됐어요</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>Class 7</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>일상·사교</t>
+          <t>협상·거래</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>How long have you been there? What's it</t>
+          <t>We've been hit by ~ before</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>신발 사업</t>
+          <t>전에 ~를 겪은 적 있어요</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>Class 7</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>일상·사교</t>
+          <t>협상·거래</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Today's Expressions #1 – 5</t>
+          <t>If ~ slips, ~ follows</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>저희는 ~ 을 전문으로 합니다</t>
+          <t>~가 밀리면 ~가 따라와요</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>Class 7</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>일상·사교</t>
+          <t>협상·거래</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>we specialize in</t>
+          <t>The estimate went from ~ to ~</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>저희는 ~ 년째 사업을 하고 있어요</t>
+          <t>견적이 ~에서 ~로 갔어요</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>Class 7</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>일상·사교</t>
+          <t>협상·거래</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>we've been in business for</t>
+          <t>The one that keeps us up is ~</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>편하게 ~ 하세요</t>
+          <t>제일 신경 쓰이는 건 ~예요</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>Class 7</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>일상·사교</t>
+          <t>협상·거래</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>feel free to</t>
+          <t>To prevent ~, we ~</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>저희가 제공하는 것은</t>
+          <t>~를 막으려고 ~해요</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>Class 7</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>일상·사교</t>
+          <t>협상·거래</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>what we offer is</t>
+          <t>We handle it by ~</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>기꺼이 ~ 해드릴게요</t>
+          <t>우리는 ~로 대응해요</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>Class 7</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>일상·사교</t>
+          <t>협상·거래</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Quiz</t>
+          <t>What I can promise is ~</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>한국어 뜻을 보고 빈칸에 알맞은 표현을 넣어보세요</t>
+          <t>제가 약속드릴 수 있는 건 ~예요</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>Class 7</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>협상·거래</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>I'd rather flag it early than ~</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>~하느니 미리 알려드리는 게 낫죠</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Class 7</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>협상·거래</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Felt much better</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Class 7</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>협상·거래</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>felt more comfortable</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Class 7</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>협상·거래</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>faith</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Class 7</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>협상·거래</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>it’s confirmed that red color will not be accepted</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Class 7</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>협상·거래</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>subjective matters when it comes to confirming colors</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Class 7</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>협상·거래</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>experts</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Class 7</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>협상·거래</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>### Notes:</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Class 7</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>협상·거래</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>continue to chase</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Class 7</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>협상·거래</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>customer sometimes don’t provide the deadline</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Class 7</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>협상·거래</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Those smaller factories</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Class 7</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>협상·거래</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>companies usually have the fixed schedule but too flexible</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Class 7</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>협상·거래</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>accompany</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Class 7</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>협상·거래</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>### Notes:</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Class 7</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>협상·거래</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>three shifts</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Class 7</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>협상·거래</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>mid-tier manager</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Class 7</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>협상·거래</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>### Notes:</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Class 7</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>협상·거래</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>For Autry, everything should be possible. Nothing can’t be promised  ### Notes:</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
           <t>Trial</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>일상·사교</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Intro &amp; Warm-Up</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>자기소개</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Trial</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Brian introduces himself — then your</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>인도네시아 생활</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Trial</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>How long have you been there? What's it</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>신발 사업</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Trial</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Today's Expressions #1 – 5</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>저희는 ~ 을 전문으로 합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Trial</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>we specialize in</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>저희는 ~ 년째 사업을 하고 있어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Trial</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>we've been in business for</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>편하게 ~ 하세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Trial</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>feel free to</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>저희가 제공하는 것은</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Trial</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>what we offer is</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>기꺼이 ~ 해드릴게요</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Trial</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Quiz</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>한국어 뜻을 보고 빈칸에 알맞은 표현을 넣어보세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Trial</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
         <is>
           <t>Fill in the Blank</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>한국어 뜻을 보고 빈칸에 알맞은 표현을 넣어보세요</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D65"/>
+  <autoFilter ref="A1:D92"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>